--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98451</v>
+        <v>98453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137158068</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137158055</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137158093</v>
       </c>
       <c r="B5" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137158047</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137158091</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137158104</v>
       </c>
       <c r="B8" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137158099</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>137158061</v>
       </c>
       <c r="B10" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98455</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96614</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137158068</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137158055</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137158093</v>
       </c>
       <c r="B5" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137158047</v>
       </c>
       <c r="B6" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137158091</v>
       </c>
       <c r="B7" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137158104</v>
       </c>
       <c r="B8" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137158099</v>
       </c>
       <c r="B9" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>137158061</v>
       </c>
       <c r="B10" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -825,11 +825,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>
@@ -1166,11 +1162,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>
@@ -1287,11 +1279,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>
@@ -1408,11 +1396,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>
@@ -1529,11 +1513,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>
@@ -1646,11 +1626,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96619</v>
+        <v>96629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137158068</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137158055</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137158093</v>
       </c>
       <c r="B5" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137158047</v>
       </c>
       <c r="B6" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137158091</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137158104</v>
       </c>
       <c r="B8" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137158099</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137158061</v>
       </c>
       <c r="B10" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98473</v>
+        <v>98483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96629</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137158068</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137158055</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137158093</v>
       </c>
       <c r="B5" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137158047</v>
       </c>
       <c r="B6" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137158091</v>
       </c>
       <c r="B7" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137158104</v>
       </c>
       <c r="B8" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137158099</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>137158061</v>
       </c>
       <c r="B10" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98484</v>
+        <v>98489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96635</v>
+        <v>96637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137158040</v>
       </c>
       <c r="B11" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137158083</v>
       </c>
       <c r="B12" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137158052</v>
       </c>
       <c r="B13" t="n">
-        <v>98489</v>
+        <v>98491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96637</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137158068</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137158055</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137158093</v>
       </c>
       <c r="B5" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137158047</v>
       </c>
       <c r="B6" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137158091</v>
       </c>
       <c r="B7" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137158104</v>
       </c>
       <c r="B8" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137158099</v>
+        <v>137390283</v>
       </c>
       <c r="B9" t="n">
-        <v>58195</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,42 +1491,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Broröd A37724-2026, Sk</t>
+          <t>Broröd, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>390017</v>
+        <v>390018</v>
       </c>
       <c r="R9" t="n">
-        <v>6220019</v>
+        <v>6220040</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,22 +1546,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,27 +1576,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137158099</t>
+          <t>https://artportalen.se/Sighting/137390283</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137158061</v>
+        <v>137158099</v>
       </c>
       <c r="B10" t="n">
-        <v>56765</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,24 +1604,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206046</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389993</v>
+        <v>390017</v>
       </c>
       <c r="R10" t="n">
-        <v>6220145</v>
+        <v>6220019</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,51 +1704,52 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137158061</t>
+          <t>https://artportalen.se/Sighting/137158099</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137158040</v>
+        <v>137158061</v>
       </c>
       <c r="B11" t="n">
-        <v>106599</v>
+        <v>56765</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221157</v>
+        <v>206046</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Broröd A37724-2026, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>390016</v>
+        <v>389993</v>
       </c>
       <c r="R11" t="n">
-        <v>6220109</v>
+        <v>6220145</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,16 +1817,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137158040</t>
+          <t>https://artportalen.se/Sighting/137158061</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137158083</v>
+        <v>137158040</v>
       </c>
       <c r="B12" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389892</v>
+        <v>390016</v>
       </c>
       <c r="R12" t="n">
-        <v>6220068</v>
+        <v>6220109</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1892,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,16 +1929,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137158083</t>
+          <t>https://artportalen.se/Sighting/137158040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137158052</v>
+        <v>137158083</v>
       </c>
       <c r="B13" t="n">
-        <v>98491</v>
+        <v>106605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222736</v>
+        <v>221157</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Majbräken</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Athyrium filix-femina</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>390005</v>
+        <v>389892</v>
       </c>
       <c r="R13" t="n">
-        <v>6220130</v>
+        <v>6220068</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2004,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,6 +2040,118 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137158083</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137158052</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98497</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Broröd A37724-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>390005</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6220130</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137158052</t>
         </is>
@@ -2058,6 +2171,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -1826,7 +1826,7 @@
         <v>137158040</v>
       </c>
       <c r="B12" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>137158083</v>
       </c>
       <c r="B13" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137158040</v>
       </c>
       <c r="B12" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>137158083</v>
       </c>
       <c r="B13" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>137158052</v>
       </c>
       <c r="B14" t="n">
-        <v>98497</v>
+        <v>98509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96655</v>
+        <v>96656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137158040</v>
       </c>
       <c r="B12" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>137158083</v>
       </c>
       <c r="B13" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>137158052</v>
       </c>
       <c r="B14" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137158040</v>
       </c>
       <c r="B12" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>137158083</v>
       </c>
       <c r="B13" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>137158052</v>
       </c>
       <c r="B14" t="n">
-        <v>98510</v>
+        <v>98513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37724-2026 artfynd.xlsx
+++ b/artfynd/A 37724-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137158063</v>
       </c>
       <c r="B2" t="n">
-        <v>96659</v>
+        <v>96663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137158068</v>
       </c>
       <c r="B3" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137158055</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137158093</v>
       </c>
       <c r="B5" t="n">
-        <v>58310</v>
+        <v>58313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137158047</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137158091</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137158104</v>
       </c>
       <c r="B8" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>137390283</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137158099</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137158061</v>
       </c>
       <c r="B11" t="n">
-        <v>56765</v>
+        <v>56768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>137158040</v>
       </c>
       <c r="B12" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>137158083</v>
       </c>
       <c r="B13" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>137158052</v>
       </c>
       <c r="B14" t="n">
-        <v>98513</v>
+        <v>98517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
